--- a/基礎演習/Chapter10.xlsx
+++ b/基礎演習/Chapter10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\村石 莉彩\Desktop\研修資料\13_Servlet・JSP\1.基礎\演習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades-2024-12-java-win-64bit-jre_20250120\workspace\Servlet\基礎演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3416E5FF-318C-4CD4-BFB8-2DF9D14D0C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5641F3B-D35D-4B33-B705-384604DED0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28635" yWindow="-6510" windowWidth="17070" windowHeight="15465" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-5775" windowWidth="17070" windowHeight="15465" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="基礎１" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="151">
   <si>
     <r>
       <rPr>
@@ -63,11 +63,11 @@
       </rPr>
       <t xml:space="preserve"> 基礎問題</t>
     </r>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>1. フィルタの動作</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>問題： Filter の動作に関する記述として 正しくないもの を選んでください。</t>
@@ -131,11 +131,11 @@
   </si>
   <si>
     <t>B. chain.doFilter(request, response); の位置</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>C. response.setCharacterEncoding("UTF-8"); の位置</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>D. すべて正しい</t>
@@ -157,7 +157,7 @@
   </si>
   <si>
     <t>5. フィルタの解除</t>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>A.</t>
@@ -219,7 +219,7 @@
       </rPr>
       <t xml:space="preserve"> 応用問題</t>
     </r>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>1. FilterChain の動作</t>
@@ -325,7 +325,7 @@
     <rPh sb="18" eb="19">
       <t>クダ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t xml:space="preserve">        long startTime = System.currentTimeMillis();</t>
@@ -350,9 +350,6 @@
   </si>
   <si>
     <t>5. FilterConfig の使用</t>
-  </si>
-  <si>
-    <t>問題： FilterConfig を使って初期パラメータを取得する正しいコードを選んでください。</t>
   </si>
   <si>
     <t>public void init(FilterConfig config) {</t>
@@ -443,29 +440,29 @@
     <rPh sb="1" eb="3">
       <t>ヨウケン</t>
     </rPh>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>Q1.フィルタで何をチェックするか?</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>Q4.なぜこの処理をサーブレットではなくフィルタに書くべきか？</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>Q2.未ログイン時の処理はどう書く？</t>
     <rPh sb="15" eb="16">
       <t>カ</t>
     </rPh>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>Q3.権限不足時の処理はどう書く？</t>
     <rPh sb="14" eb="15">
       <t>カ</t>
     </rPh>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>次の要件を満たすフィルタ設計を考えなさい。</t>
@@ -481,15 +478,15 @@
   </si>
   <si>
     <t>Q1.この処理は何個のフィルタに分けるべきか？</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>Q2.フィルタの処理順はどうなるか？</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>Q3.chain.doFilter() の前後で何を書くか？</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>問題： jakarta.servlet.Filter インターフェースの 必須メソッド として 含まれない ものを選んでください。</t>
@@ -514,14 +511,14 @@
   </si>
   <si>
     <t>LogFilter.java … フィルタ本体</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>【ログ出力形式】</t>
     <rPh sb="3" eb="7">
       <t>シュツリョクケイシキ</t>
     </rPh>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>[LOG] アクセスURL: /Chapter9_Answer_Besic02/index.jsp</t>
@@ -546,51 +543,63 @@
   </si>
   <si>
     <t>A</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>D</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>B</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>問題： web.xml に複数のフィルタを設定する場合、実行順序は どのように決まるか？</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>C</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>問題： フィルタの適用を 特定の URL のみ解除 するための web.xml の設定として正しいものを選んでください。</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>・LogFilter.java を作成すること</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>・リクエストのたびに「[LOG] アクセスURL: /xxx」の形式でコンソールに出力すること</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
   </si>
   <si>
     <t>index.jsp　　 … 動作確認用ページ</t>
-    <phoneticPr fontId="6"/>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>問題： FilterConfig を使って初期パラメータを取得する正しいコードを選んでください。</t>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -751,40 +760,43 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
@@ -1110,7 +1122,7 @@
         <v>5</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1125,7 +1137,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="B11" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1143,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1290,7 +1302,7 @@
         <v>22</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1310,7 +1322,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="B34" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1328,7 +1340,7 @@
         <v>28</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1343,7 +1355,7 @@
     </row>
     <row r="41" spans="1:9">
       <c r="B41" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1496,7 +1508,7 @@
       <c r="F58" s="6"/>
       <c r="G58" s="7"/>
       <c r="J58" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59" spans="2:10">
@@ -1585,7 +1597,7 @@
       <c r="G68" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6"/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1597,96 +1609,96 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6"/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1960,6 +1972,9 @@
       <c r="B25" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="H25" s="13" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1">
       <c r="B26" s="1" t="s">
@@ -1998,7 +2013,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
     </row>
-    <row r="33" spans="1:7" s="1" customFormat="1">
+    <row r="33" spans="1:12" s="1" customFormat="1">
       <c r="B33" s="5" t="s">
         <v>34</v>
       </c>
@@ -2008,7 +2023,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
     </row>
-    <row r="34" spans="1:7" s="1" customFormat="1">
+    <row r="34" spans="1:12" s="1" customFormat="1">
       <c r="B34" s="5" t="s">
         <v>35</v>
       </c>
@@ -2018,7 +2033,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="7"/>
     </row>
-    <row r="35" spans="1:7" s="1" customFormat="1">
+    <row r="35" spans="1:12" s="1" customFormat="1">
       <c r="B35" s="5" t="s">
         <v>36</v>
       </c>
@@ -2028,7 +2043,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="7"/>
     </row>
-    <row r="36" spans="1:7" s="1" customFormat="1">
+    <row r="36" spans="1:12" s="1" customFormat="1">
       <c r="B36" s="5" t="s">
         <v>33</v>
       </c>
@@ -2038,7 +2053,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="7"/>
     </row>
-    <row r="37" spans="1:7" s="1" customFormat="1">
+    <row r="37" spans="1:12" s="1" customFormat="1">
       <c r="B37" s="5" t="s">
         <v>62</v>
       </c>
@@ -2048,7 +2063,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="7"/>
     </row>
-    <row r="38" spans="1:7" s="1" customFormat="1">
+    <row r="38" spans="1:12" s="1" customFormat="1">
       <c r="B38" s="8" t="s">
         <v>39</v>
       </c>
@@ -2057,46 +2072,49 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="10"/>
-    </row>
-    <row r="39" spans="1:7" s="1" customFormat="1"/>
-    <row r="40" spans="1:7" s="1" customFormat="1">
+      <c r="L38" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="1" customFormat="1"/>
+    <row r="40" spans="1:12" s="1" customFormat="1">
       <c r="B40" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1">
+    <row r="41" spans="1:12" s="1" customFormat="1">
       <c r="B41" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="1" customFormat="1">
+    <row r="42" spans="1:12" s="1" customFormat="1">
       <c r="B42" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="1" customFormat="1">
+    <row r="43" spans="1:12" s="1" customFormat="1">
       <c r="B43" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="1" customFormat="1"/>
-    <row r="45" spans="1:7" s="1" customFormat="1">
+    <row r="44" spans="1:12" s="1" customFormat="1"/>
+    <row r="45" spans="1:12" s="1" customFormat="1">
       <c r="A45" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="1" customFormat="1">
+    <row r="46" spans="1:12" s="1" customFormat="1">
       <c r="B46" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="1" customFormat="1"/>
-    <row r="48" spans="1:7" s="1" customFormat="1">
+    <row r="47" spans="1:12" s="1" customFormat="1"/>
+    <row r="48" spans="1:12" s="1" customFormat="1">
       <c r="B48" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:8" s="1" customFormat="1">
+    <row r="49" spans="1:11" s="1" customFormat="1">
       <c r="B49" s="2" t="s">
         <v>69</v>
       </c>
@@ -2107,7 +2125,7 @@
       <c r="G49" s="3"/>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:8" s="1" customFormat="1">
+    <row r="50" spans="1:11" s="1" customFormat="1">
       <c r="B50" s="8" t="s">
         <v>70</v>
       </c>
@@ -2118,13 +2136,13 @@
       <c r="G50" s="9"/>
       <c r="H50" s="10"/>
     </row>
-    <row r="51" spans="1:8" s="1" customFormat="1"/>
-    <row r="52" spans="1:8" s="1" customFormat="1">
+    <row r="51" spans="1:11" s="1" customFormat="1"/>
+    <row r="52" spans="1:11" s="1" customFormat="1">
       <c r="B52" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:8" s="1" customFormat="1">
+    <row r="53" spans="1:11" s="1" customFormat="1">
       <c r="B53" s="2" t="s">
         <v>71</v>
       </c>
@@ -2135,7 +2153,7 @@
       <c r="G53" s="3"/>
       <c r="H53" s="4"/>
     </row>
-    <row r="54" spans="1:8" s="1" customFormat="1">
+    <row r="54" spans="1:11" s="1" customFormat="1">
       <c r="B54" s="8" t="s">
         <v>70</v>
       </c>
@@ -2146,13 +2164,13 @@
       <c r="G54" s="9"/>
       <c r="H54" s="10"/>
     </row>
-    <row r="55" spans="1:8" s="1" customFormat="1"/>
-    <row r="56" spans="1:8" s="1" customFormat="1">
+    <row r="55" spans="1:11" s="1" customFormat="1"/>
+    <row r="56" spans="1:11" s="1" customFormat="1">
       <c r="B56" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:8" s="1" customFormat="1">
+    <row r="57" spans="1:11" s="1" customFormat="1">
       <c r="B57" s="2" t="s">
         <v>72</v>
       </c>
@@ -2163,7 +2181,7 @@
       <c r="G57" s="3"/>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" spans="1:8" s="1" customFormat="1">
+    <row r="58" spans="1:11" s="1" customFormat="1">
       <c r="B58" s="8" t="s">
         <v>70</v>
       </c>
@@ -2173,25 +2191,28 @@
       <c r="F58" s="9"/>
       <c r="G58" s="9"/>
       <c r="H58" s="10"/>
-    </row>
-    <row r="59" spans="1:8" s="1" customFormat="1"/>
-    <row r="60" spans="1:8" s="1" customFormat="1">
+      <c r="K58" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" s="1" customFormat="1"/>
+    <row r="60" spans="1:11" s="1" customFormat="1">
       <c r="B60" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="61" spans="1:8" s="1" customFormat="1">
+    <row r="61" spans="1:11" s="1" customFormat="1">
       <c r="B61" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="1:8" s="1" customFormat="1">
+    <row r="62" spans="1:11" s="1" customFormat="1">
       <c r="B62" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:8" s="1" customFormat="1"/>
-    <row r="64" spans="1:8" s="1" customFormat="1">
+    <row r="63" spans="1:11" s="1" customFormat="1"/>
+    <row r="64" spans="1:11" s="1" customFormat="1">
       <c r="A64" s="1" t="s">
         <v>75</v>
       </c>
@@ -2352,6 +2373,9 @@
       <c r="B77" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="L77" s="13" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="78" spans="1:14" s="1" customFormat="1">
       <c r="B78" s="1" t="s">
@@ -2365,8 +2389,8 @@
       </c>
     </row>
     <row r="81" spans="2:7" s="1" customFormat="1">
-      <c r="B81" s="1" t="s">
-        <v>85</v>
+      <c r="B81" s="13" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="2:7" s="1" customFormat="1"/>
@@ -2377,7 +2401,7 @@
     </row>
     <row r="84" spans="2:7" s="1" customFormat="1">
       <c r="B84" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
@@ -2387,7 +2411,7 @@
     </row>
     <row r="85" spans="2:7" s="1" customFormat="1">
       <c r="B85" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
@@ -2412,7 +2436,7 @@
     </row>
     <row r="88" spans="2:7" s="1" customFormat="1">
       <c r="B88" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
@@ -2422,7 +2446,7 @@
     </row>
     <row r="89" spans="2:7" s="1" customFormat="1">
       <c r="B89" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
@@ -2447,7 +2471,7 @@
     </row>
     <row r="92" spans="2:7" s="1" customFormat="1">
       <c r="B92" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
@@ -2457,7 +2481,7 @@
     </row>
     <row r="93" spans="2:7" s="1" customFormat="1">
       <c r="B93" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C93" s="6"/>
       <c r="D93" s="6"/>
@@ -2482,7 +2506,7 @@
     </row>
     <row r="96" spans="2:7" s="1" customFormat="1">
       <c r="B96" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
@@ -2490,17 +2514,20 @@
       <c r="F96" s="3"/>
       <c r="G96" s="4"/>
     </row>
-    <row r="97" spans="2:7" s="1" customFormat="1">
+    <row r="97" spans="2:9" s="1" customFormat="1">
       <c r="B97" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
       <c r="G97" s="7"/>
-    </row>
-    <row r="98" spans="2:7" s="1" customFormat="1">
+      <c r="I97" s="13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" s="1" customFormat="1">
       <c r="B98" s="8" t="s">
         <v>20</v>
       </c>
@@ -2510,10 +2537,10 @@
       <c r="F98" s="9"/>
       <c r="G98" s="10"/>
     </row>
-    <row r="99" spans="2:7" s="1" customFormat="1"/>
-    <row r="100" spans="2:7" s="1" customFormat="1"/>
+    <row r="99" spans="2:9" s="1" customFormat="1"/>
+    <row r="100" spans="2:9" s="1" customFormat="1"/>
   </sheetData>
-  <phoneticPr fontId="6"/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2525,66 +2552,66 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="C4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="C5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6"/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2596,51 +2623,51 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="C4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="C5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="B8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6"/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2653,103 +2680,105 @@
     <row r="1" spans="2:3" s="1" customFormat="1"/>
     <row r="2" spans="2:3" s="1" customFormat="1">
       <c r="B2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="2:3" s="1" customFormat="1">
       <c r="C3" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="2:3" s="1" customFormat="1"/>
     <row r="5" spans="2:3" s="1" customFormat="1">
       <c r="B5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="2:3" s="1" customFormat="1">
       <c r="C6" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="2:3" s="1" customFormat="1">
       <c r="C7" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="2:3" s="1" customFormat="1">
       <c r="C8" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="2:3" s="1" customFormat="1">
       <c r="C9" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="2:3" s="1" customFormat="1">
       <c r="C10" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="2:3" s="1" customFormat="1">
       <c r="C11" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="2:3" s="1" customFormat="1">
       <c r="C12" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="2:3" s="1" customFormat="1">
       <c r="C13" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="2:3" s="1" customFormat="1">
       <c r="C14" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="2:3" s="1" customFormat="1"/>
     <row r="16" spans="2:3" s="1" customFormat="1">
       <c r="B16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="3:3" s="1" customFormat="1">
       <c r="C17" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="3:3" s="1" customFormat="1">
       <c r="C18" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6"/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2960,20 +2989,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{600182C4-80E6-4001-9475-71B4D528AC1B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A3F5117-088C-4B41-9E04-E0B07D646DA3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
+    <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2998,12 +3028,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A3F5117-088C-4B41-9E04-E0B07D646DA3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{600182C4-80E6-4001-9475-71B4D528AC1B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
-    <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>